--- a/data/trans_camb/IP18A03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27,78</t>
+          <t>38,11</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,26</t>
+          <t>22,41</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20,03</t>
+          <t>30,26</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 37,05</t>
+          <t>8,36; 38,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,15; 43,95</t>
+          <t>15,5; 44,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 48,1</t>
+          <t>11,87; 55,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 17,83</t>
+          <t>-12,87; 16,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 17,91</t>
+          <t>-10,72; 18,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 31,64</t>
+          <t>2,02; 36,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 23,84</t>
+          <t>2,32; 22,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 26,79</t>
+          <t>5,91; 26,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 33,95</t>
+          <t>14,0; 41,58</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,06; 104,58</t>
+          <t>16,83; 107,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,18; 123,12</t>
+          <t>28,77; 122,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 127,27</t>
+          <t>27,72; 153,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 31,14</t>
+          <t>-17,47; 29,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 31,14</t>
+          <t>-14,75; 32,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 52,2</t>
+          <t>4,58; 65,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 48,43</t>
+          <t>3,84; 45,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,23; 54,06</t>
+          <t>9,47; 53,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 68,55</t>
+          <t>24,57; 84,08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-19,31</t>
+          <t>13,19</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-11,46</t>
+          <t>24,64</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-15,15</t>
+          <t>19,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 10,28</t>
+          <t>-10,98; 10,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 14,58</t>
+          <t>-6,58; 13,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-43,2; 3,7</t>
+          <t>-8,44; 27,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 17,55</t>
+          <t>-2,35; 17,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 14,18</t>
+          <t>-5,1; 15,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,76; 10,75</t>
+          <t>11,64; 34,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 10,83</t>
+          <t>-4,11; 12,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 10,91</t>
+          <t>-2,75; 11,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 0,32</t>
+          <t>8,08; 27,23</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-26,85%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-16,81%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-21,64%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 15,41</t>
+          <t>-14,37; 15,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 22,31</t>
+          <t>-8,56; 20,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,65; 4,79</t>
+          <t>-11,22; 40,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 27,71</t>
+          <t>-3,08; 27,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 22,47</t>
+          <t>-6,95; 24,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,71; 16,29</t>
+          <t>16,69; 56,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 16,77</t>
+          <t>-5,42; 19,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 16,61</t>
+          <t>-3,67; 18,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,56; 0,58</t>
+          <t>11,64; 40,91</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-56,85</t>
+          <t>12,19</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-73,94</t>
+          <t>15,44</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-66,1</t>
+          <t>13,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-31,34; -4,35</t>
+          <t>-32,67; -3,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 9,13</t>
+          <t>-18,51; 8,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-71,08; -33,77</t>
+          <t>-10,09; 25,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-30,94; -6,04</t>
+          <t>-31,11; -6,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 15,86</t>
+          <t>-7,36; 15,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-81,93; -64,55</t>
+          <t>-3,26; 27,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-27,64; -9,2</t>
+          <t>-27,38; -9,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 9,12</t>
+          <t>-8,75; 9,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-73,67; -52,79</t>
+          <t>0,37; 23,71</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-76,24%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-89,04%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,79; -6,26</t>
+          <t>-42,03; -6,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 13,19</t>
+          <t>-23,04; 12,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-92,96; -45,08</t>
+          <t>-11,98; 37,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,07; -9,57</t>
+          <t>-39,83; -9,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 23,55</t>
+          <t>-9,15; 23,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,1; 40,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-35,76; -13,42</t>
+          <t>-35,36; -12,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 12,91</t>
+          <t>-11,39; 13,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-96,87; -72,58</t>
+          <t>0,66; 33,62</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-42,82</t>
+          <t>13,33</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-37,15</t>
+          <t>21,89</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-39,81</t>
+          <t>17,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,51; 29,06</t>
+          <t>4,29; 28,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 22,48</t>
+          <t>-5,94; 20,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-61,35; -12,79</t>
+          <t>-16,35; 32,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 25,62</t>
+          <t>0,36; 26,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 21,41</t>
+          <t>-5,64; 20,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-64,08; 8,51</t>
+          <t>-0,9; 35,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,69; 24,01</t>
+          <t>6,98; 23,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 17,12</t>
+          <t>-1,43; 16,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-57,26; -14,87</t>
+          <t>0,86; 30,04</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-66,5%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-56,64%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-61,25%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,02; 52,25</t>
+          <t>6,04; 50,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 38,88</t>
+          <t>-8,15; 36,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-90,45; -19,51</t>
+          <t>-22,24; 53,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,72; 45,04</t>
+          <t>0,56; 46,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 37,79</t>
+          <t>-7,71; 34,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 12,7</t>
+          <t>-0,1; 62,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,69; 40,21</t>
+          <t>10,34; 38,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 28,99</t>
+          <t>-1,93; 28,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-85,48; -20,05</t>
+          <t>1,12; 48,13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-8,41</t>
+          <t>43,02</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-27,48</t>
+          <t>21,05</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-18,14</t>
+          <t>31,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29,71; 63,13</t>
+          <t>31,85; 64,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,03; 47,22</t>
+          <t>11,35; 48,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-41,45; 36,49</t>
+          <t>-0,88; 64,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 36,06</t>
+          <t>1,36; 35,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 23,82</t>
+          <t>-13,58; 25,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-54,92; 9,33</t>
+          <t>-17,58; 43,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,18; 44,25</t>
+          <t>20,57; 44,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 29,79</t>
+          <t>4,87; 30,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-40,62; 11,64</t>
+          <t>4,81; 50,23</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-20,18%</t>
+          <t>103,24%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-47,24%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-36,34%</t>
+          <t>63,33%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>53,52; 212,31</t>
+          <t>58,71; 233,54</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22,52; 161,32</t>
+          <t>22,23; 180,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 104,42</t>
+          <t>7,57; 199,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,27; 79,79</t>
+          <t>1,84; 78,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,0; 49,26</t>
+          <t>-20,05; 57,7</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-85,63; 20,34</t>
+          <t>-23,89; 91,93</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,82; 106,7</t>
+          <t>34,28; 108,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>7,88; 70,99</t>
+          <t>8,64; 77,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 25,84</t>
+          <t>11,87; 118,78</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-56,39</t>
+          <t>7,65</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-63,94</t>
+          <t>12,84</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-62,1</t>
+          <t>10,24</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-34,36; -5,78</t>
+          <t>-33,74; -4,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 7,34</t>
+          <t>-19,81; 8,41</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-74,52; -29,31</t>
+          <t>-19,34; 24,49</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-36,02; -5,1</t>
+          <t>-36,33; -4,95</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 14,32</t>
+          <t>-14,57; 13,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-76,02; -46,4</t>
+          <t>-6,22; 27,85</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-31,44; -9,97</t>
+          <t>-31,39; -10,61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 5,58</t>
+          <t>-13,1; 6,75</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-72,1; -47,36</t>
+          <t>-4,24; 21,39</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-74,29%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-90,43%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-84,71%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-43,16; -8,97</t>
+          <t>-42,03; -7,08</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 10,47</t>
+          <t>-24,81; 11,95</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-93,19; -38,09</t>
+          <t>-24,06; 35,72</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-47,15; -8,66</t>
+          <t>-47,83; -8,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 23,65</t>
+          <t>-18,66; 23,16</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -64,64</t>
+          <t>-7,79; 45,6</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-40,8; -15,0</t>
+          <t>-40,98; -15,65</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 7,97</t>
+          <t>-17,24; 9,81</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-94,51; -66,29</t>
+          <t>-5,81; 30,12</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-32,47</t>
+          <t>7,95</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-41,5</t>
+          <t>11,75</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-37,61</t>
+          <t>9,92</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-28,18; -8,7</t>
+          <t>-28,07; -9,37</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-36,46; -15,93</t>
+          <t>-35,89; -15,42</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-51,95; -7,33</t>
+          <t>-12,0; 23,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-21,78; -2,55</t>
+          <t>-22,5; -2,66</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-30,0; -9,57</t>
+          <t>-30,62; -9,8</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-56,82; -23,59</t>
+          <t>-4,59; 24,46</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-22,3; -8,61</t>
+          <t>-23,02; -9,25</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-30,51; -15,28</t>
+          <t>-30,71; -15,98</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-49,54; -20,73</t>
+          <t>-1,78; 20,69</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-46,45%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-61,85%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-54,92%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-38,34; -13,36</t>
+          <t>-38,51; -14,79</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-49,61; -24,4</t>
+          <t>-49,35; -24,4</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-73,24; -10,63</t>
+          <t>-16,45; 34,56</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-30,77; -4,27</t>
+          <t>-31,49; -4,27</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-41,93; -15,18</t>
+          <t>-43,59; -15,32</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-81,99; -34,54</t>
+          <t>-6,06; 38,97</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-31,12; -13,64</t>
+          <t>-32,4; -14,36</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-43,18; -23,59</t>
+          <t>-42,76; -24,32</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-71,52; -31,63</t>
+          <t>-2,64; 30,74</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-12,42</t>
+          <t>-8,09</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-12,77</t>
+          <t>-6,18</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-12,34</t>
+          <t>-6,6</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>6,79; 26,04</t>
+          <t>6,18; 26,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3,16; 22,83</t>
+          <t>2,68; 22,09</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-34,0; 12,18</t>
+          <t>-28,5; 14,48</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8,91; 27,44</t>
+          <t>9,58; 26,37</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 16,77</t>
+          <t>-0,39; 17,27</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-29,55; 9,62</t>
+          <t>-24,72; 13,29</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,3; 23,64</t>
+          <t>10,51; 23,97</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,62; 17,41</t>
+          <t>3,61; 17,52</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-24,99; 4,39</t>
+          <t>-20,11; 9,52</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-25,27%</t>
+          <t>-16,46%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-24,46%</t>
+          <t>-11,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-24,3%</t>
+          <t>-12,99%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>12,13; 60,69</t>
+          <t>11,4; 62,62</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>5,72; 52,46</t>
+          <t>4,72; 51,29</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-66,06; 26,06</t>
+          <t>-55,76; 31,58</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15,41; 58,34</t>
+          <t>16,96; 58,35</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 35,77</t>
+          <t>-0,64; 36,22</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-55,9; 19,28</t>
+          <t>-46,27; 26,8</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,04; 51,14</t>
+          <t>18,96; 51,26</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>6,52; 37,27</t>
+          <t>6,55; 37,38</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-47,88; 9,07</t>
+          <t>-38,25; 19,77</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-25,77</t>
+          <t>14,29</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-32,33</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-29,4</t>
+          <t>14,85</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 6,68</t>
+          <t>-2,05; 6,82</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 6,82</t>
+          <t>-2,34; 6,79</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-34,43; -16,73</t>
+          <t>6,32; 21,55</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 5,79</t>
+          <t>-2,49; 5,83</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 4,65</t>
+          <t>-3,93; 4,69</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-39,51; -24,62</t>
+          <t>8,26; 20,89</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,86</t>
+          <t>-1,24; 4,89</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 4,55</t>
+          <t>-1,67; 4,41</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-35,59; -22,61</t>
+          <t>9,67; 19,68</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-41,03%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-50,24%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-46,23%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 10,87</t>
+          <t>-3,25; 11,21</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 11,3</t>
+          <t>-3,4; 11,38</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-53,83; -27,21</t>
+          <t>9,46; 34,97</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 9,29</t>
+          <t>-3,8; 9,42</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 7,54</t>
+          <t>-5,82; 7,59</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-60,72; -38,42</t>
+          <t>12,52; 33,61</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 7,83</t>
+          <t>-1,69; 8,11</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 7,31</t>
+          <t>-2,53; 7,15</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-55,46; -36,14</t>
+          <t>15,1; 31,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 38,46</t>
+          <t>8,41; 39,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,5; 44,33</t>
+          <t>14,6; 44,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,87; 55,81</t>
+          <t>11,37; 55,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 16,86</t>
+          <t>-13,28; 16,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 18,18</t>
+          <t>-10,87; 17,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 36,46</t>
+          <t>1,86; 37,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 22,88</t>
+          <t>1,96; 23,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,91; 26,67</t>
+          <t>6,78; 28,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,0; 41,58</t>
+          <t>15,65; 41,98</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,83; 107,68</t>
+          <t>16,37; 110,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,77; 122,59</t>
+          <t>26,89; 123,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,72; 153,11</t>
+          <t>28,56; 153,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 29,86</t>
+          <t>-17,78; 28,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 32,0</t>
+          <t>-15,01; 31,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 65,79</t>
+          <t>2,8; 63,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 45,45</t>
+          <t>3,7; 48,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,47; 53,02</t>
+          <t>11,09; 58,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,57; 84,08</t>
+          <t>26,44; 84,23</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 10,51</t>
+          <t>-11,6; 10,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 13,96</t>
+          <t>-6,98; 13,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 27,8</t>
+          <t>-10,93; 28,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 17,08</t>
+          <t>-3,55; 16,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 15,76</t>
+          <t>-5,09; 15,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,64; 34,51</t>
+          <t>11,67; 34,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 12,45</t>
+          <t>-3,31; 11,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 11,76</t>
+          <t>-3,64; 12,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,08; 27,23</t>
+          <t>6,39; 27,62</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 15,85</t>
+          <t>-15,09; 15,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 20,63</t>
+          <t>-9,0; 20,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 40,36</t>
+          <t>-15,59; 40,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 27,66</t>
+          <t>-4,82; 27,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 24,7</t>
+          <t>-6,73; 25,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,69; 56,61</t>
+          <t>17,26; 56,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 19,08</t>
+          <t>-4,45; 17,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 18,16</t>
+          <t>-4,83; 18,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,64; 40,91</t>
+          <t>9,47; 41,74</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-32,67; -3,74</t>
+          <t>-32,99; -5,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 8,31</t>
+          <t>-18,49; 8,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 25,9</t>
+          <t>-6,64; 26,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-31,11; -6,05</t>
+          <t>-31,55; -5,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 15,88</t>
+          <t>-7,23; 15,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 27,1</t>
+          <t>-2,62; 27,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-27,38; -9,26</t>
+          <t>-28,04; -8,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 9,3</t>
+          <t>-8,83; 9,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 23,71</t>
+          <t>0,67; 24,05</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,03; -6,15</t>
+          <t>-40,6; -7,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 12,16</t>
+          <t>-22,95; 13,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 37,32</t>
+          <t>-7,81; 39,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,83; -9,23</t>
+          <t>-39,94; -8,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 23,78</t>
+          <t>-8,86; 24,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 40,52</t>
+          <t>-2,87; 40,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-35,36; -12,95</t>
+          <t>-36,43; -12,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 13,48</t>
+          <t>-11,43; 12,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 33,62</t>
+          <t>1,4; 34,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,29; 28,53</t>
+          <t>4,64; 29,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 20,34</t>
+          <t>-5,13; 22,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 32,09</t>
+          <t>-16,03; 34,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 26,45</t>
+          <t>2,58; 27,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 20,39</t>
+          <t>-5,17; 21,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 35,72</t>
+          <t>-1,15; 35,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,98; 23,28</t>
+          <t>6,37; 23,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 16,99</t>
+          <t>-1,06; 17,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 30,04</t>
+          <t>0,18; 30,67</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,04; 50,36</t>
+          <t>7,65; 53,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 36,37</t>
+          <t>-7,22; 39,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 53,11</t>
+          <t>-23,48; 58,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 46,18</t>
+          <t>3,59; 47,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 34,64</t>
+          <t>-6,88; 36,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 62,18</t>
+          <t>0,32; 62,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,34; 38,79</t>
+          <t>8,95; 40,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 28,54</t>
+          <t>-1,6; 29,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 48,13</t>
+          <t>0,25; 50,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31,85; 64,95</t>
+          <t>32,92; 64,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,35; 48,05</t>
+          <t>10,34; 46,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 64,48</t>
+          <t>-9,0; 64,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 35,04</t>
+          <t>0,14; 36,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 25,39</t>
+          <t>-12,2; 23,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 43,66</t>
+          <t>-17,22; 43,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,57; 44,98</t>
+          <t>21,62; 44,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,87; 30,74</t>
+          <t>5,02; 30,63</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,81; 50,23</t>
+          <t>7,48; 48,6</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>58,71; 233,54</t>
+          <t>61,93; 239,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22,23; 180,14</t>
+          <t>21,63; 164,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7,57; 199,82</t>
+          <t>1,74; 209,02</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,84; 78,1</t>
+          <t>0,36; 80,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 57,7</t>
+          <t>-18,23; 52,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 91,93</t>
+          <t>-25,17; 92,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,28; 108,09</t>
+          <t>37,18; 109,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8,64; 77,04</t>
+          <t>8,5; 77,12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11,87; 118,78</t>
+          <t>17,51; 113,96</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-33,74; -4,0</t>
+          <t>-36,04; -5,55</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 8,41</t>
+          <t>-20,64; 9,21</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 24,49</t>
+          <t>-19,14; 22,69</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-36,33; -4,95</t>
+          <t>-35,3; -6,12</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 13,93</t>
+          <t>-13,15; 13,85</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 27,85</t>
+          <t>-6,42; 27,3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-31,39; -10,61</t>
+          <t>-30,95; -11,02</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 6,75</t>
+          <t>-13,17; 6,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 21,39</t>
+          <t>-4,28; 22,25</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-42,03; -7,08</t>
+          <t>-44,03; -7,55</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 11,95</t>
+          <t>-25,47; 13,41</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 35,72</t>
+          <t>-23,47; 32,43</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-47,83; -8,57</t>
+          <t>-46,72; -9,69</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 23,16</t>
+          <t>-17,87; 22,02</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 45,6</t>
+          <t>-7,23; 43,78</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-40,98; -15,65</t>
+          <t>-40,36; -16,09</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 9,81</t>
+          <t>-16,73; 9,68</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 30,12</t>
+          <t>-5,29; 33,37</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-28,07; -9,37</t>
+          <t>-27,7; -7,98</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-35,89; -15,42</t>
+          <t>-36,34; -15,51</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 23,15</t>
+          <t>-10,98; 23,97</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-22,5; -2,66</t>
+          <t>-22,83; -1,82</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-30,62; -9,8</t>
+          <t>-30,62; -9,31</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 24,46</t>
+          <t>-7,4; 25,41</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-23,02; -9,25</t>
+          <t>-22,52; -8,35</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-30,71; -15,98</t>
+          <t>-30,32; -16,31</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 20,69</t>
+          <t>-1,85; 20,2</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-38,51; -14,79</t>
+          <t>-37,64; -12,26</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-49,35; -24,4</t>
+          <t>-48,77; -23,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 34,56</t>
+          <t>-15,44; 34,77</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-31,49; -4,27</t>
+          <t>-31,48; -3,47</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-43,59; -15,32</t>
+          <t>-43,04; -14,65</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 38,97</t>
+          <t>-8,48; 40,36</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-32,4; -14,36</t>
+          <t>-31,58; -12,93</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-42,76; -24,32</t>
+          <t>-42,92; -24,56</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 30,74</t>
+          <t>-2,64; 30,99</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>6,18; 26,73</t>
+          <t>6,98; 26,06</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,68; 22,09</t>
+          <t>4,21; 22,34</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 14,48</t>
+          <t>-29,47; 15,73</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9,58; 26,37</t>
+          <t>9,79; 27,01</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 17,27</t>
+          <t>-1,56; 16,72</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 13,29</t>
+          <t>-25,71; 14,19</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,51; 23,97</t>
+          <t>10,65; 23,68</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,61; 17,52</t>
+          <t>3,76; 16,69</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 9,52</t>
+          <t>-20,9; 9,31</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>11,4; 62,62</t>
+          <t>13,37; 60,35</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4,72; 51,29</t>
+          <t>7,78; 51,93</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-55,76; 31,58</t>
+          <t>-57,99; 35,07</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16,96; 58,35</t>
+          <t>17,04; 57,56</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 36,22</t>
+          <t>-2,8; 35,24</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-46,27; 26,8</t>
+          <t>-46,86; 28,39</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,96; 51,26</t>
+          <t>19,28; 50,96</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>6,55; 37,38</t>
+          <t>7,09; 36,13</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 19,77</t>
+          <t>-39,77; 19,04</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 6,82</t>
+          <t>-2,13; 6,94</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 6,79</t>
+          <t>-1,84; 6,97</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6,32; 21,55</t>
+          <t>5,84; 21,44</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 5,83</t>
+          <t>-2,84; 5,89</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,69</t>
+          <t>-3,48; 4,77</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,26; 20,89</t>
+          <t>8,61; 21,31</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,89</t>
+          <t>-1,12; 4,85</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 4,41</t>
+          <t>-1,65; 4,18</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9,67; 19,68</t>
+          <t>9,58; 20,05</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 11,21</t>
+          <t>-3,29; 11,35</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 11,38</t>
+          <t>-2,84; 11,62</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>9,46; 34,97</t>
+          <t>9,32; 35,39</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 9,42</t>
+          <t>-4,27; 9,44</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 7,59</t>
+          <t>-5,33; 7,64</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12,52; 33,61</t>
+          <t>13,08; 34,03</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 8,11</t>
+          <t>-1,7; 7,83</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 7,15</t>
+          <t>-2,56; 6,7</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>15,1; 31,39</t>
+          <t>14,58; 31,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A03-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,62</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21,94</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>23,79</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>30,32</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>38,11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,69</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,62</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,41</t>
+          <t>37,49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30,26</t>
+          <t>29,65</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,41; 39,08</t>
+          <t>-12,36; 17,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,6; 44,36</t>
+          <t>-10,55; 17,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,37; 55,21</t>
+          <t>1,07; 36,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 16,5</t>
+          <t>6,03; 37,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 17,93</t>
+          <t>14,15; 43,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 37,08</t>
+          <t>8,27; 54,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 23,49</t>
+          <t>2,14; 23,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 28,53</t>
+          <t>6,56; 26,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,65; 41,98</t>
+          <t>13,36; 42,66</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>33,49%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>52,8%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>67,3%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>84,57%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>53,46%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,37; 110,55</t>
+          <t>-17,24; 31,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,89; 123,56</t>
+          <t>-14,43; 31,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,56; 153,11</t>
+          <t>2,57; 61,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 28,95</t>
+          <t>12,06; 104,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 31,28</t>
+          <t>26,18; 123,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 63,9</t>
+          <t>24,47; 150,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 48,16</t>
+          <t>3,54; 48,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,09; 58,82</t>
+          <t>11,23; 54,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,44; 84,23</t>
+          <t>23,75; 86,92</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,41</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,02</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25,69</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,42</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13,19</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,41</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,02</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,64</t>
+          <t>12,49</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19,31</t>
+          <t>19,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 10,63</t>
+          <t>-2,76; 17,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 13,58</t>
+          <t>-5,48; 14,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 28,0</t>
+          <t>13,64; 34,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 16,92</t>
+          <t>-12,03; 10,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 15,84</t>
+          <t>-6,16; 14,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,67; 34,25</t>
+          <t>-10,83; 27,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 11,81</t>
+          <t>-3,35; 10,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 12,04</t>
+          <t>-3,02; 10,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,39; 27,62</t>
+          <t>7,35; 27,78</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,86%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37,68%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-0,14%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>4,76%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18,35%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 15,72</t>
+          <t>-3,85; 27,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 20,61</t>
+          <t>-7,39; 22,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 40,22</t>
+          <t>19,47; 55,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 27,63</t>
+          <t>-15,65; 15,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 25,63</t>
+          <t>-8,12; 22,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,26; 56,58</t>
+          <t>-15,1; 39,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 17,88</t>
+          <t>-4,48; 16,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 18,24</t>
+          <t>-4,06; 16,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 41,74</t>
+          <t>10,67; 41,68</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-18,7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,55</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16,07</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-18,98</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,67</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12,19</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-18,7</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,55</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,44</t>
+          <t>12,38</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,93</t>
+          <t>14,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-32,99; -5,5</t>
+          <t>-30,94; -6,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 8,61</t>
+          <t>-7,64; 15,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 26,39</t>
+          <t>-0,46; 29,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-31,55; -5,45</t>
+          <t>-31,34; -4,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 15,79</t>
+          <t>-17,16; 9,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 27,8</t>
+          <t>-8,22; 25,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-28,04; -8,89</t>
+          <t>-27,64; -9,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 9,19</t>
+          <t>-8,83; 9,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 24,05</t>
+          <t>2,93; 23,94</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-25,29%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21,73%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-25,46%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-6,27%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16,34%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-25,29%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,6; -7,89</t>
+          <t>-40,07; -9,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 13,05</t>
+          <t>-9,78; 23,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 39,02</t>
+          <t>-0,6; 44,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,94; -8,23</t>
+          <t>-39,79; -6,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 24,09</t>
+          <t>-21,31; 13,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 40,68</t>
+          <t>-10,65; 37,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,43; -12,82</t>
+          <t>-35,76; -13,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 12,8</t>
+          <t>-11,14; 12,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 34,39</t>
+          <t>3,94; 34,25</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13,7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7,87</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23,12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>16,84</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>8,37</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13,33</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13,7</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,87</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,89</t>
+          <t>10,22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17,86</t>
+          <t>16,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,64; 29,95</t>
+          <t>2,47; 25,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 22,14</t>
+          <t>-4,68; 21,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 34,24</t>
+          <t>3,33; 36,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 27,21</t>
+          <t>5,51; 29,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 21,01</t>
+          <t>-4,01; 22,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 35,78</t>
+          <t>-17,23; 32,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,37; 23,93</t>
+          <t>6,69; 24,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 17,33</t>
+          <t>-1,45; 17,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 30,67</t>
+          <t>-1,67; 29,45</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>20,88%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>35,25%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>26,15%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>12,99%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>20,69%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>20,88%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>12,0%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,65; 53,97</t>
+          <t>3,72; 45,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 39,14</t>
+          <t>-6,25; 37,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 58,75</t>
+          <t>5,52; 64,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,59; 47,95</t>
+          <t>8,02; 52,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 36,47</t>
+          <t>-5,94; 38,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 62,43</t>
+          <t>-26,8; 55,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,95; 40,74</t>
+          <t>8,69; 40,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 29,01</t>
+          <t>-2,14; 28,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 50,03</t>
+          <t>-2,45; 48,63</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>18,43</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5,67</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>20,74</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>48,79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>29,92</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>43,02</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>18,43</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5,67</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,05</t>
+          <t>43,29</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>31,62</t>
+          <t>31,65</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32,92; 64,3</t>
+          <t>-0,32; 36,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,34; 46,21</t>
+          <t>-13,54; 23,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 64,68</t>
+          <t>-16,97; 44,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 36,07</t>
+          <t>29,71; 63,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 23,87</t>
+          <t>12,03; 47,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 43,93</t>
+          <t>4,46; 67,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,62; 44,61</t>
+          <t>20,18; 44,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,02; 30,63</t>
+          <t>4,53; 29,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,48; 48,6</t>
+          <t>6,03; 49,72</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>31,69%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>35,66%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>117,08%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>71,82%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>103,24%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>103,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,4%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>61,93; 239,45</t>
+          <t>0,27; 79,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>21,63; 164,04</t>
+          <t>-20,0; 49,26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1,74; 209,02</t>
+          <t>-25,8; 90,39</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,36; 80,05</t>
+          <t>53,52; 212,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 52,11</t>
+          <t>22,52; 161,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 92,17</t>
+          <t>14,94; 222,6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,18; 109,57</t>
+          <t>33,82; 106,7</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8,5; 77,12</t>
+          <t>7,88; 70,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17,51; 113,96</t>
+          <t>16,0; 118,33</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-21,65</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-0,71</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>10,79</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-20,35</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-6,05</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>7,65</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-21,65</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,84</t>
+          <t>9,5</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10,24</t>
+          <t>9,68</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-36,04; -5,55</t>
+          <t>-36,02; -5,1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 9,21</t>
+          <t>-14,0; 14,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 22,69</t>
+          <t>-11,18; 27,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-35,3; -6,12</t>
+          <t>-34,36; -5,78</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 13,85</t>
+          <t>-19,58; 7,34</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 27,3</t>
+          <t>-12,91; 26,1</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-30,95; -11,02</t>
+          <t>-31,44; -9,97</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 6,8</t>
+          <t>-13,4; 5,58</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 22,25</t>
+          <t>-5,4; 22,59</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-30,62%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-1,0%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>15,26%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-26,81%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-7,98%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>10,07%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-30,62%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-1,0%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-44,03; -7,55</t>
+          <t>-47,15; -8,66</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-25,47; 13,41</t>
+          <t>-18,45; 23,65</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 32,43</t>
+          <t>-13,52; 42,25</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-46,72; -9,69</t>
+          <t>-43,16; -8,97</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 22,02</t>
+          <t>-23,78; 10,47</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 43,78</t>
+          <t>-15,84; 37,73</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-40,36; -16,09</t>
+          <t>-40,8; -15,0</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 9,68</t>
+          <t>-17,22; 7,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 33,37</t>
+          <t>-6,11; 33,7</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-12,74</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-20,15</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>12,38</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-18,46</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-26,71</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>7,95</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-12,74</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-20,15</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,75</t>
+          <t>4,09</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9,92</t>
+          <t>8,71</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-27,7; -7,98</t>
+          <t>-21,78; -2,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-36,34; -15,51</t>
+          <t>-30,0; -9,57</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 23,97</t>
+          <t>-4,67; 24,48</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-22,83; -1,82</t>
+          <t>-28,18; -8,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-30,62; -9,31</t>
+          <t>-36,46; -15,93</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 25,41</t>
+          <t>-16,88; 19,01</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-22,52; -8,35</t>
+          <t>-22,3; -8,61</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-30,32; -16,31</t>
+          <t>-30,51; -15,28</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 20,2</t>
+          <t>-4,85; 19,08</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-18,99%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-30,02%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>18,45%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-26,42%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-38,22%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-18,99%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-30,02%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-37,64; -12,26</t>
+          <t>-30,77; -4,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-48,77; -23,79</t>
+          <t>-41,93; -15,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 34,77</t>
+          <t>-5,99; 38,53</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-31,48; -3,47</t>
+          <t>-38,34; -13,36</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-43,04; -14,65</t>
+          <t>-49,61; -24,4</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 40,36</t>
+          <t>-21,75; 28,56</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-31,58; -12,93</t>
+          <t>-31,12; -13,64</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-42,92; -24,56</t>
+          <t>-43,18; -23,59</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 30,99</t>
+          <t>-6,77; 28,54</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>18,21</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>7,95</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-5,53</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>16,49</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>13,16</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-8,09</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>18,21</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>7,95</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-6,18</t>
+          <t>-11,66</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-6,6</t>
+          <t>-7,47</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>6,98; 26,06</t>
+          <t>8,91; 27,44</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4,21; 22,34</t>
+          <t>-1,85; 16,77</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 15,73</t>
+          <t>-23,96; 17,02</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9,79; 27,01</t>
+          <t>6,79; 26,04</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 16,72</t>
+          <t>3,16; 22,83</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-25,71; 14,19</t>
+          <t>-32,85; 12,35</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,65; 23,68</t>
+          <t>10,3; 23,64</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,76; 16,69</t>
+          <t>3,62; 17,41</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 9,31</t>
+          <t>-21,52; 9,51</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>34,85%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>15,22%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-10,59%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>33,54%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>26,77%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-16,46%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>34,85%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>15,22%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-11,84%</t>
+          <t>-23,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-12,99%</t>
+          <t>-14,72%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>13,37; 60,35</t>
+          <t>15,41; 58,34</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7,78; 51,93</t>
+          <t>-3,13; 35,77</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-57,99; 35,07</t>
+          <t>-44,21; 32,38</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17,04; 57,56</t>
+          <t>12,13; 60,69</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 35,24</t>
+          <t>5,72; 52,46</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 28,39</t>
+          <t>-66,91; 25,27</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,28; 50,96</t>
+          <t>19,04; 51,14</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>7,09; 36,13</t>
+          <t>6,52; 37,27</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-39,77; 19,04</t>
+          <t>-41,05; 20,98</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>1,47</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>0,53</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>14,87</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>2,41</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>2,26</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>14,29</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>12,75</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>14,85</t>
+          <t>14,02</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 6,94</t>
+          <t>-2,68; 5,79</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,97</t>
+          <t>-4,07; 4,65</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5,84; 21,44</t>
+          <t>7,8; 21,15</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 5,89</t>
+          <t>-2,24; 6,68</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 4,77</t>
+          <t>-2,03; 6,82</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,61; 21,31</t>
+          <t>3,9; 20,14</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,85</t>
+          <t>-1,24; 4,86</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,18</t>
+          <t>-1,62; 4,55</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9,58; 20,05</t>
+          <t>8,23; 18,7</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>23,11%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>3,6%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>22,75%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 11,35</t>
+          <t>-4,09; 9,29</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 11,62</t>
+          <t>-6,16; 7,54</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>9,32; 35,39</t>
+          <t>11,66; 33,85</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 9,44</t>
+          <t>-3,44; 10,87</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 7,64</t>
+          <t>-3,09; 11,3</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>13,08; 34,03</t>
+          <t>6,21; 33,29</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 7,83</t>
+          <t>-1,9; 7,83</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 6,7</t>
+          <t>-2,5; 7,31</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>14,58; 31,81</t>
+          <t>12,82; 29,97</t>
         </is>
       </c>
     </row>
